--- a/data/trans_bre/P74B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,77</t>
+          <t>0,0; 60,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 39,8</t>
+          <t>-3,96; 40,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 6,0</t>
+          <t>-31,06; 5,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,56</t>
+          <t>-6,08; -0,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,29; 35,81</t>
+          <t>15,13; 35,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 22,16</t>
+          <t>1,28; 21,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 772,58</t>
+          <t>-3,6; 732,31</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 43,78</t>
+          <t>17,6; 44,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 22,11</t>
+          <t>6,97; 21,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 24,8</t>
+          <t>7,73; 23,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121,75; 837,81</t>
+          <t>103,14; 878,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,64; 888,53</t>
+          <t>106,24; 913,62</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,62; 79,58</t>
+          <t>57,2; 79,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,44; 49,64</t>
+          <t>30,34; 49,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 31,11</t>
+          <t>15,33; 32,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1441,54; 8574,78</t>
+          <t>1379,79; 7832,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>501,24; 2903,83</t>
+          <t>522,41; 2375,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>214,91; 1014,9</t>
+          <t>199,25; 1027,21</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,34; 84,86</t>
+          <t>73,07; 84,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,99; 81,83</t>
+          <t>69,53; 81,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,9; 79,05</t>
+          <t>64,95; 78,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>614,08; 1527,26</t>
+          <t>620,27; 1573,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>529,0; 1401,2</t>
+          <t>535,61; 1398,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>536,96; 1406,78</t>
+          <t>532,31; 1443,15</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,09; 82,1</t>
+          <t>71,0; 81,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,29; 74,08</t>
+          <t>60,3; 74,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,89; 77,03</t>
+          <t>65,39; 77,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>296,58; 567,2</t>
+          <t>300,98; 566,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>170,72; 322,14</t>
+          <t>172,45; 325,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>191,34; 343,91</t>
+          <t>193,16; 361,01</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,85; 82,64</t>
+          <t>66,63; 83,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,28; 71,55</t>
+          <t>55,75; 71,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,76; 75,55</t>
+          <t>61,84; 75,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>269,63; 616,11</t>
+          <t>253,21; 610,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>125,82; 252,57</t>
+          <t>128,44; 255,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>174,02; 329,71</t>
+          <t>172,03; 317,53</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>71,91; 78,22</t>
+          <t>71,58; 78,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,29; 58,99</t>
+          <t>51,8; 59,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,88; 57,51</t>
+          <t>49,85; 57,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>810,39; 1228,21</t>
+          <t>803,46; 1228,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>366,32; 545,53</t>
+          <t>363,35; 533,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>363,85; 527,04</t>
+          <t>358,18; 518,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P74B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,96</t>
+          <t>0,0; 52,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 40,41</t>
+          <t>-4,11; 41,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 5,77</t>
+          <t>-30,55; 6,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -0,55</t>
+          <t>-6,1; -0,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 35,4</t>
+          <t>14,96; 36,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 21,08</t>
+          <t>1,48; 23,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 732,31</t>
+          <t>-1,69; 821,37</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 44,88</t>
+          <t>17,62; 44,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 21,93</t>
+          <t>7,25; 21,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 23,62</t>
+          <t>7,84; 24,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>103,14; 878,28</t>
+          <t>129,15; 892,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>106,24; 913,62</t>
+          <t>111,51; 884,12</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,2; 79,8</t>
+          <t>56,85; 79,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,34; 49,62</t>
+          <t>30,52; 50,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 32,26</t>
+          <t>15,32; 32,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1379,79; 7832,91</t>
+          <t>1274,78; 8293,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>522,41; 2375,92</t>
+          <t>520,49; 2251,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>199,25; 1027,21</t>
+          <t>202,73; 1030,46</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,07; 84,55</t>
+          <t>72,97; 85,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,53; 81,44</t>
+          <t>69,25; 82,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,95; 78,55</t>
+          <t>64,47; 79,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>620,27; 1573,13</t>
+          <t>634,4; 1596,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>535,61; 1398,63</t>
+          <t>532,49; 1439,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>532,31; 1443,15</t>
+          <t>522,16; 1410,1</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,0; 81,99</t>
+          <t>70,64; 82,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,3; 74,11</t>
+          <t>60,58; 74,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65,39; 77,69</t>
+          <t>65,26; 77,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>300,98; 566,13</t>
+          <t>296,46; 567,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>172,45; 325,31</t>
+          <t>173,13; 331,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193,16; 361,01</t>
+          <t>195,05; 351,9</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,63; 83,12</t>
+          <t>66,92; 83,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,75; 71,57</t>
+          <t>55,8; 71,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,84; 75,08</t>
+          <t>61,37; 75,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>253,21; 610,89</t>
+          <t>262,44; 625,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>128,44; 255,36</t>
+          <t>128,53; 254,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>172,03; 317,53</t>
+          <t>171,2; 338,72</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>71,58; 78,49</t>
+          <t>71,72; 78,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,8; 59,19</t>
+          <t>51,66; 59,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,85; 57,32</t>
+          <t>50,14; 57,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>803,46; 1228,43</t>
+          <t>802,34; 1210,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>363,35; 533,68</t>
+          <t>357,72; 529,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>358,18; 518,0</t>
+          <t>352,6; 512,46</t>
         </is>
       </c>
     </row>
